--- a/survey_templates/046_image_annotation_survey--survey_templates.xlsx
+++ b/survey_templates/046_image_annotation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_terms_and_conditions',_'value':_'agree'}</t>
+          <t>i_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the terms and conditions', 'value': 'agree'}</t>
+          <t>I agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree_to_the_terms_and_conditions',_'value':_'disagree'}</t>
+          <t>i_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I do not agree to the terms and conditions', 'value': 'disagree'}</t>
+          <t>I do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'classification',_'value':_'classification'}</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Classification', 'value': 'classification'}</t>
+          <t>Classification</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'identification',_'value':_'identification'}</t>
+          <t>identification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Identification', 'value': 'identification'}</t>
+          <t>Identification</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'object_detection',_'value':_'object_detection'}</t>
+          <t>object_detection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Object Detection', 'value': 'object_detection'}</t>
+          <t>Object Detection</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'segmentation',_'value':_'segmentation'}</t>
+          <t>segmentation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Segmentation', 'value': 'segmentation'}</t>
+          <t>Segmentation</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_started',_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started', 'value': 'not_started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
